--- a/SyncLogs/SynchronizeLogNewEntries - tasks.xlsx
+++ b/SyncLogs/SynchronizeLogNewEntries - tasks.xlsx
@@ -20,6 +20,84 @@
     <t>cell_address</t>
   </si>
   <si>
+    <t>40,5</t>
+  </si>
+  <si>
+    <t>40,6</t>
+  </si>
+  <si>
+    <t>41,5</t>
+  </si>
+  <si>
+    <t>48,5</t>
+  </si>
+  <si>
+    <t>48,6</t>
+  </si>
+  <si>
+    <t>49,5</t>
+  </si>
+  <si>
+    <t>49,6</t>
+  </si>
+  <si>
+    <t>50,5</t>
+  </si>
+  <si>
+    <t>50,6</t>
+  </si>
+  <si>
+    <t>51,5</t>
+  </si>
+  <si>
+    <t>51,6</t>
+  </si>
+  <si>
+    <t>52,5</t>
+  </si>
+  <si>
+    <t>52,6</t>
+  </si>
+  <si>
+    <t>18,6</t>
+  </si>
+  <si>
+    <t>19,5</t>
+  </si>
+  <si>
+    <t>19,6</t>
+  </si>
+  <si>
+    <t>20,5</t>
+  </si>
+  <si>
+    <t>20,6</t>
+  </si>
+  <si>
+    <t>21,5</t>
+  </si>
+  <si>
+    <t>21,6</t>
+  </si>
+  <si>
+    <t>22,5</t>
+  </si>
+  <si>
+    <t>22,6</t>
+  </si>
+  <si>
+    <t>23,5</t>
+  </si>
+  <si>
+    <t>23,6</t>
+  </si>
+  <si>
+    <t>24,5</t>
+  </si>
+  <si>
+    <t>24,6</t>
+  </si>
+  <si>
     <t>3,5</t>
   </si>
   <si>
@@ -35,43 +113,43 @@
     <t>5,5</t>
   </si>
   <si>
-    <t>18,6</t>
-  </si>
-  <si>
-    <t>19,5</t>
-  </si>
-  <si>
-    <t>19,6</t>
-  </si>
-  <si>
-    <t>20,5</t>
-  </si>
-  <si>
-    <t>20,6</t>
-  </si>
-  <si>
-    <t>21,5</t>
-  </si>
-  <si>
-    <t>21,6</t>
-  </si>
-  <si>
-    <t>22,5</t>
-  </si>
-  <si>
-    <t>22,6</t>
-  </si>
-  <si>
-    <t>23,5</t>
-  </si>
-  <si>
-    <t>23,6</t>
-  </si>
-  <si>
-    <t>24,5</t>
-  </si>
-  <si>
-    <t>24,6</t>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>6,5</t>
+  </si>
+  <si>
+    <t>6,6</t>
+  </si>
+  <si>
+    <t>7,5</t>
+  </si>
+  <si>
+    <t>7,6</t>
+  </si>
+  <si>
+    <t>8,5</t>
+  </si>
+  <si>
+    <t>8,6</t>
+  </si>
+  <si>
+    <t>9,5</t>
+  </si>
+  <si>
+    <t>9,6</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>10,6</t>
+  </si>
+  <si>
+    <t>11,5</t>
+  </si>
+  <si>
+    <t>18,5</t>
   </si>
   <si>
     <t>25,5</t>
@@ -86,43 +164,43 @@
     <t>33,5</t>
   </si>
   <si>
-    <t>40,5</t>
-  </si>
-  <si>
-    <t>40,6</t>
-  </si>
-  <si>
-    <t>41,5</t>
-  </si>
-  <si>
-    <t>48,5</t>
-  </si>
-  <si>
-    <t>48,6</t>
-  </si>
-  <si>
-    <t>49,5</t>
-  </si>
-  <si>
-    <t>49,6</t>
-  </si>
-  <si>
-    <t>50,5</t>
-  </si>
-  <si>
-    <t>50,6</t>
-  </si>
-  <si>
-    <t>51,5</t>
-  </si>
-  <si>
-    <t>51,6</t>
-  </si>
-  <si>
-    <t>52,5</t>
-  </si>
-  <si>
-    <t>52,6</t>
+    <t>33,6</t>
+  </si>
+  <si>
+    <t>34,5</t>
+  </si>
+  <si>
+    <t>34,6</t>
+  </si>
+  <si>
+    <t>35,5</t>
+  </si>
+  <si>
+    <t>35,6</t>
+  </si>
+  <si>
+    <t>36,5</t>
+  </si>
+  <si>
+    <t>36,6</t>
+  </si>
+  <si>
+    <t>37,5</t>
+  </si>
+  <si>
+    <t>37,6</t>
+  </si>
+  <si>
+    <t>38,5</t>
+  </si>
+  <si>
+    <t>38,6</t>
+  </si>
+  <si>
+    <t>39,5</t>
+  </si>
+  <si>
+    <t>39,6</t>
   </si>
   <si>
     <t>53,5</t>
@@ -137,6 +215,15 @@
     <t>54,6</t>
   </si>
   <si>
+    <t>55,5</t>
+  </si>
+  <si>
+    <t>55,6</t>
+  </si>
+  <si>
+    <t>56,5</t>
+  </si>
+  <si>
     <t>56,6</t>
   </si>
   <si>
@@ -257,45 +344,6 @@
     <t>11,6</t>
   </si>
   <si>
-    <t>5,6</t>
-  </si>
-  <si>
-    <t>6,5</t>
-  </si>
-  <si>
-    <t>6,6</t>
-  </si>
-  <si>
-    <t>7,5</t>
-  </si>
-  <si>
-    <t>7,6</t>
-  </si>
-  <si>
-    <t>8,5</t>
-  </si>
-  <si>
-    <t>8,6</t>
-  </si>
-  <si>
-    <t>9,5</t>
-  </si>
-  <si>
-    <t>9,6</t>
-  </si>
-  <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>10,6</t>
-  </si>
-  <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>18,5</t>
-  </si>
-  <si>
     <t>12,5</t>
   </si>
   <si>
@@ -332,54 +380,6 @@
     <t>17,6</t>
   </si>
   <si>
-    <t>33,6</t>
-  </si>
-  <si>
-    <t>34,5</t>
-  </si>
-  <si>
-    <t>34,6</t>
-  </si>
-  <si>
-    <t>35,5</t>
-  </si>
-  <si>
-    <t>35,6</t>
-  </si>
-  <si>
-    <t>36,5</t>
-  </si>
-  <si>
-    <t>36,6</t>
-  </si>
-  <si>
-    <t>37,5</t>
-  </si>
-  <si>
-    <t>37,6</t>
-  </si>
-  <si>
-    <t>38,5</t>
-  </si>
-  <si>
-    <t>38,6</t>
-  </si>
-  <si>
-    <t>39,5</t>
-  </si>
-  <si>
-    <t>39,6</t>
-  </si>
-  <si>
-    <t>55,5</t>
-  </si>
-  <si>
-    <t>55,6</t>
-  </si>
-  <si>
-    <t>56,5</t>
-  </si>
-  <si>
     <t>cell_address2</t>
   </si>
   <si>
@@ -464,6 +464,48 @@
     <t>time_slice</t>
   </si>
   <si>
+    <t>S02WD2P</t>
+  </si>
+  <si>
+    <t>S02WD2Y</t>
+  </si>
+  <si>
+    <t>S03WD2F</t>
+  </si>
+  <si>
+    <t>S03WD2G</t>
+  </si>
+  <si>
+    <t>S03WD2P</t>
+  </si>
+  <si>
+    <t>S03WD2Y</t>
+  </si>
+  <si>
+    <t>S03WD2Z</t>
+  </si>
+  <si>
+    <t>S01WD2F</t>
+  </si>
+  <si>
+    <t>S01WD2G</t>
+  </si>
+  <si>
+    <t>S01WD2P</t>
+  </si>
+  <si>
+    <t>S01WD2Y</t>
+  </si>
+  <si>
+    <t>S01WD2Z</t>
+  </si>
+  <si>
+    <t>S02WD1A</t>
+  </si>
+  <si>
+    <t>S02WD1B</t>
+  </si>
+  <si>
     <t>S01WD1A</t>
   </si>
   <si>
@@ -473,25 +515,22 @@
     <t>S01WD1C</t>
   </si>
   <si>
-    <t>S01WD2F</t>
-  </si>
-  <si>
-    <t>S01WD2G</t>
-  </si>
-  <si>
-    <t>S01WD2P</t>
-  </si>
-  <si>
-    <t>S01WD2Y</t>
-  </si>
-  <si>
-    <t>S01WD2Z</t>
-  </si>
-  <si>
-    <t>S02WD1A</t>
-  </si>
-  <si>
-    <t>S02WD1B</t>
+    <t>S01WD1D</t>
+  </si>
+  <si>
+    <t>S01WD1E</t>
+  </si>
+  <si>
+    <t>S01WD1F</t>
+  </si>
+  <si>
+    <t>S01WD1G</t>
+  </si>
+  <si>
+    <t>S01WD1P</t>
+  </si>
+  <si>
+    <t>S01WD1Y</t>
   </si>
   <si>
     <t>S02WD1C</t>
@@ -503,25 +542,22 @@
     <t>S02WD2A</t>
   </si>
   <si>
-    <t>S02WD2P</t>
-  </si>
-  <si>
-    <t>S02WD2Y</t>
-  </si>
-  <si>
-    <t>S03WD2F</t>
-  </si>
-  <si>
-    <t>S03WD2G</t>
-  </si>
-  <si>
-    <t>S03WD2P</t>
-  </si>
-  <si>
-    <t>S03WD2Y</t>
-  </si>
-  <si>
-    <t>S03WD2Z</t>
+    <t>S02WD2B</t>
+  </si>
+  <si>
+    <t>S02WD2C</t>
+  </si>
+  <si>
+    <t>S02WD2D</t>
+  </si>
+  <si>
+    <t>S02WD2E</t>
+  </si>
+  <si>
+    <t>S02WD2F</t>
+  </si>
+  <si>
+    <t>S02WD2G</t>
   </si>
   <si>
     <t>S03WD1A</t>
@@ -530,6 +566,9 @@
     <t>S03WD1B</t>
   </si>
   <si>
+    <t>S03WD1C</t>
+  </si>
+  <si>
     <t>S03WD1D</t>
   </si>
   <si>
@@ -587,24 +626,6 @@
     <t>S02WD1Z</t>
   </si>
   <si>
-    <t>S01WD1Y</t>
-  </si>
-  <si>
-    <t>S01WD1D</t>
-  </si>
-  <si>
-    <t>S01WD1E</t>
-  </si>
-  <si>
-    <t>S01WD1F</t>
-  </si>
-  <si>
-    <t>S01WD1G</t>
-  </si>
-  <si>
-    <t>S01WD1P</t>
-  </si>
-  <si>
     <t>S01WD1Z</t>
   </si>
   <si>
@@ -623,27 +644,6 @@
     <t>S01WD2E</t>
   </si>
   <si>
-    <t>S02WD2B</t>
-  </si>
-  <si>
-    <t>S02WD2C</t>
-  </si>
-  <si>
-    <t>S02WD2D</t>
-  </si>
-  <si>
-    <t>S02WD2E</t>
-  </si>
-  <si>
-    <t>S02WD2F</t>
-  </si>
-  <si>
-    <t>S02WD2G</t>
-  </si>
-  <si>
-    <t>S03WD1C</t>
-  </si>
-  <si>
     <t>time_slice2</t>
   </si>
   <si>
@@ -716,15 +716,15 @@
     <t>ACT_UPS</t>
   </si>
   <si>
+    <t>ACT_MINLD</t>
+  </si>
+  <si>
     <t>ACT_TIME</t>
   </si>
   <si>
     <t>ACT_CSTSD</t>
   </si>
   <si>
-    <t>ACT_MINLD</t>
-  </si>
-  <si>
     <t>MessageCategory</t>
   </si>
   <si>
@@ -749,105 +749,105 @@
     <t>48,23</t>
   </si>
   <si>
+    <t>18,3</t>
+  </si>
+  <si>
+    <t>33,3</t>
+  </si>
+  <si>
+    <t>17,10</t>
+  </si>
+  <si>
+    <t>31,10</t>
+  </si>
+  <si>
+    <t>33,23</t>
+  </si>
+  <si>
+    <t>17,23</t>
+  </si>
+  <si>
+    <t>25,1</t>
+  </si>
+  <si>
+    <t>17,3</t>
+  </si>
+  <si>
+    <t>48,3</t>
+  </si>
+  <si>
+    <t>18,17</t>
+  </si>
+  <si>
+    <t>29,23</t>
+  </si>
+  <si>
+    <t>18,23</t>
+  </si>
+  <si>
+    <t>29,17</t>
+  </si>
+  <si>
+    <t>48,10</t>
+  </si>
+  <si>
+    <t>33,29</t>
+  </si>
+  <si>
+    <t>18,10</t>
+  </si>
+  <si>
+    <t>48,29</t>
+  </si>
+  <si>
+    <t>29,3</t>
+  </si>
+  <si>
+    <t>7,1</t>
+  </si>
+  <si>
+    <t>29,10</t>
+  </si>
+  <si>
+    <t>18,29</t>
+  </si>
+  <si>
+    <t>17,17</t>
+  </si>
+  <si>
+    <t>16,1</t>
+  </si>
+  <si>
+    <t>deleted_from_veda_data</t>
+  </si>
+  <si>
     <t>29,29</t>
   </si>
   <si>
+    <t>17,29</t>
+  </si>
+  <si>
+    <t>31,17</t>
+  </si>
+  <si>
+    <t>31,3</t>
+  </si>
+  <si>
+    <t>31,29</t>
+  </si>
+  <si>
     <t>33,17</t>
   </si>
   <si>
-    <t>17,23</t>
-  </si>
-  <si>
-    <t>18,23</t>
-  </si>
-  <si>
-    <t>17,10</t>
-  </si>
-  <si>
-    <t>31,17</t>
-  </si>
-  <si>
-    <t>25,1</t>
-  </si>
-  <si>
-    <t>18,10</t>
-  </si>
-  <si>
-    <t>17,29</t>
+    <t>31,23</t>
   </si>
   <si>
     <t>33,10</t>
   </si>
   <si>
-    <t>29,23</t>
-  </si>
-  <si>
-    <t>deleted_from_veda_data</t>
-  </si>
-  <si>
-    <t>33,23</t>
-  </si>
-  <si>
-    <t>29,17</t>
-  </si>
-  <si>
-    <t>17,3</t>
-  </si>
-  <si>
-    <t>48,10</t>
-  </si>
-  <si>
-    <t>29,3</t>
-  </si>
-  <si>
-    <t>18,17</t>
-  </si>
-  <si>
-    <t>18,29</t>
-  </si>
-  <si>
-    <t>31,23</t>
-  </si>
-  <si>
-    <t>31,3</t>
-  </si>
-  <si>
-    <t>33,29</t>
-  </si>
-  <si>
     <t>48,17</t>
   </si>
   <si>
-    <t>18,3</t>
-  </si>
-  <si>
-    <t>31,10</t>
-  </si>
-  <si>
-    <t>17,17</t>
-  </si>
-  <si>
-    <t>7,1</t>
-  </si>
-  <si>
-    <t>29,10</t>
-  </si>
-  <si>
-    <t>16,1</t>
-  </si>
-  <si>
-    <t>48,3</t>
-  </si>
-  <si>
-    <t>48,29</t>
-  </si>
-  <si>
-    <t>33,3</t>
-  </si>
-  <si>
-    <t>31,29</t>
-  </si>
-  <si>
     <t>TagType</t>
   </si>
   <si>
@@ -860,22 +860,22 @@
     <t>{"pset_pn": "E-PEA-WO4"}</t>
   </si>
   <si>
+    <t>{"pset_pn": "E-PEA-ED5"}</t>
+  </si>
+  <si>
+    <t>{"pset_pn": "E-NGA-NW5"}</t>
+  </si>
+  <si>
+    <t>{"pset_pn": "E-PEA-ED3"}</t>
+  </si>
+  <si>
+    <t>{"pset_pn": "E-COA-MP2"}</t>
+  </si>
+  <si>
+    <t>{"pset_pn": "E*HFO*,E*DIS*"}</t>
+  </si>
+  <si>
     <t>{"pset_pn": "E-PEA-LR4"}</t>
-  </si>
-  <si>
-    <t>{"pset_pn": "E-NGA-NW5"}</t>
-  </si>
-  <si>
-    <t>{"pset_pn": "E-PEA-ED3"}</t>
-  </si>
-  <si>
-    <t>{"pset_pn": "E-PEA-ED5"}</t>
-  </si>
-  <si>
-    <t>{"pset_pn": "E-COA-MP2"}</t>
-  </si>
-  <si>
-    <t>{"pset_pn": "E*HFO*,E*DIS*"}</t>
   </si>
   <si>
     <t>CommodityFilter</t>
@@ -1224,7 +1224,7 @@
         <v>124</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.053937877</v>
+        <v>0.006738811</v>
       </c>
       <c r="AC2" t="s">
         <v>217</v>
@@ -1319,7 +1319,7 @@
         <v>124</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.045285979</v>
+        <v>0.006931423</v>
       </c>
       <c r="AC3" t="s">
         <v>217</v>
@@ -1414,7 +1414,7 @@
         <v>124</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009470893</v>
+        <v>0.006423248</v>
       </c>
       <c r="AC4" t="s">
         <v>217</v>
@@ -1461,7 +1461,7 @@
         <v>134</v>
       </c>
       <c r="L5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M5" t="s">
         <v>124</v>
@@ -1494,7 +1494,7 @@
         <v>124</v>
       </c>
       <c r="W5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X5" t="s">
         <v>124</v>
@@ -1509,7 +1509,7 @@
         <v>124</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.010118339</v>
+        <v>0.002444422</v>
       </c>
       <c r="AC5" t="s">
         <v>217</v>
@@ -1556,7 +1556,7 @@
         <v>134</v>
       </c>
       <c r="L6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M6" t="s">
         <v>124</v>
@@ -1604,7 +1604,7 @@
         <v>124</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009772012</v>
+        <v>0.001969919</v>
       </c>
       <c r="AC6" t="s">
         <v>217</v>
@@ -1651,7 +1651,7 @@
         <v>134</v>
       </c>
       <c r="L7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M7" t="s">
         <v>124</v>
@@ -1699,7 +1699,7 @@
         <v>124</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004516368</v>
+        <v>0.002498876</v>
       </c>
       <c r="AC7" t="s">
         <v>217</v>
@@ -1746,7 +1746,7 @@
         <v>134</v>
       </c>
       <c r="L8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M8" t="s">
         <v>124</v>
@@ -1779,7 +1779,7 @@
         <v>124</v>
       </c>
       <c r="W8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="X8" t="s">
         <v>124</v>
@@ -1794,7 +1794,7 @@
         <v>124</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004193503</v>
+        <v>0.002380284</v>
       </c>
       <c r="AC8" t="s">
         <v>217</v>
@@ -1841,7 +1841,7 @@
         <v>134</v>
       </c>
       <c r="L9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s">
         <v>124</v>
@@ -1889,7 +1889,7 @@
         <v>124</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004690154</v>
+        <v>0.002438007</v>
       </c>
       <c r="AC9" t="s">
         <v>217</v>
@@ -1936,7 +1936,7 @@
         <v>134</v>
       </c>
       <c r="L10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s">
         <v>124</v>
@@ -1969,7 +1969,7 @@
         <v>124</v>
       </c>
       <c r="W10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X10" t="s">
         <v>124</v>
@@ -1984,7 +1984,7 @@
         <v>124</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00416601</v>
+        <v>0.002537856</v>
       </c>
       <c r="AC10" t="s">
         <v>217</v>
@@ -2031,7 +2031,7 @@
         <v>134</v>
       </c>
       <c r="L11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M11" t="s">
         <v>124</v>
@@ -2079,7 +2079,7 @@
         <v>124</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.004582276</v>
+        <v>0.002326722</v>
       </c>
       <c r="AC11" t="s">
         <v>217</v>
@@ -2126,7 +2126,7 @@
         <v>134</v>
       </c>
       <c r="L12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s">
         <v>124</v>
@@ -2159,7 +2159,7 @@
         <v>124</v>
       </c>
       <c r="W12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X12" t="s">
         <v>124</v>
@@ -2174,7 +2174,7 @@
         <v>124</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.004127151</v>
+        <v>0.002350475</v>
       </c>
       <c r="AC12" t="s">
         <v>217</v>
@@ -2221,7 +2221,7 @@
         <v>134</v>
       </c>
       <c r="L13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s">
         <v>124</v>
@@ -2269,7 +2269,7 @@
         <v>124</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.004342057</v>
+        <v>0.008188906</v>
       </c>
       <c r="AC13" t="s">
         <v>217</v>
@@ -2316,7 +2316,7 @@
         <v>134</v>
       </c>
       <c r="L14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s">
         <v>124</v>
@@ -2349,7 +2349,7 @@
         <v>124</v>
       </c>
       <c r="W14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X14" t="s">
         <v>124</v>
@@ -2364,7 +2364,7 @@
         <v>124</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.016337457</v>
+        <v>0.007518359</v>
       </c>
       <c r="AC14" t="s">
         <v>217</v>
@@ -2459,7 +2459,7 @@
         <v>124</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.013371994</v>
+        <v>0.004516368</v>
       </c>
       <c r="AC15" t="s">
         <v>217</v>
@@ -2554,7 +2554,7 @@
         <v>124</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.080785628</v>
+        <v>0.004193503</v>
       </c>
       <c r="AC16" t="s">
         <v>217</v>
@@ -2649,7 +2649,7 @@
         <v>124</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.065697347</v>
+        <v>0.004690154</v>
       </c>
       <c r="AC17" t="s">
         <v>217</v>
@@ -2744,7 +2744,7 @@
         <v>124</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.014058032</v>
+        <v>0.00416601</v>
       </c>
       <c r="AC18" t="s">
         <v>217</v>
@@ -2839,7 +2839,7 @@
         <v>124</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.01394809</v>
+        <v>0.004582276</v>
       </c>
       <c r="AC19" t="s">
         <v>217</v>
@@ -2934,7 +2934,7 @@
         <v>124</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.014288217</v>
+        <v>0.004127151</v>
       </c>
       <c r="AC20" t="s">
         <v>217</v>
@@ -3029,7 +3029,7 @@
         <v>124</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.015222432</v>
+        <v>0.004342057</v>
       </c>
       <c r="AC21" t="s">
         <v>217</v>
@@ -3124,7 +3124,7 @@
         <v>124</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.014039795</v>
+        <v>0.016337457</v>
       </c>
       <c r="AC22" t="s">
         <v>217</v>
@@ -3171,7 +3171,7 @@
         <v>134</v>
       </c>
       <c r="L23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s">
         <v>124</v>
@@ -3204,7 +3204,7 @@
         <v>124</v>
       </c>
       <c r="W23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X23" t="s">
         <v>124</v>
@@ -3219,7 +3219,7 @@
         <v>124</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.031932413</v>
+        <v>0.013371994</v>
       </c>
       <c r="AC23" t="s">
         <v>217</v>
@@ -3299,7 +3299,7 @@
         <v>124</v>
       </c>
       <c r="W24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X24" t="s">
         <v>124</v>
@@ -3314,7 +3314,7 @@
         <v>124</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.006738811</v>
+        <v>0.080785628</v>
       </c>
       <c r="AC24" t="s">
         <v>217</v>
@@ -3394,7 +3394,7 @@
         <v>124</v>
       </c>
       <c r="W25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X25" t="s">
         <v>124</v>
@@ -3409,7 +3409,7 @@
         <v>124</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.006931423</v>
+        <v>0.065697347</v>
       </c>
       <c r="AC25" t="s">
         <v>217</v>
@@ -3489,7 +3489,7 @@
         <v>124</v>
       </c>
       <c r="W26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X26" t="s">
         <v>124</v>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.006423248</v>
+        <v>0.014058032</v>
       </c>
       <c r="AC26" t="s">
         <v>217</v>
@@ -3551,7 +3551,7 @@
         <v>134</v>
       </c>
       <c r="L27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M27" t="s">
         <v>124</v>
@@ -3584,7 +3584,7 @@
         <v>124</v>
       </c>
       <c r="W27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X27" t="s">
         <v>124</v>
@@ -3599,7 +3599,7 @@
         <v>124</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.002444422</v>
+        <v>0.01394809</v>
       </c>
       <c r="AC27" t="s">
         <v>217</v>
@@ -3646,7 +3646,7 @@
         <v>134</v>
       </c>
       <c r="L28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M28" t="s">
         <v>124</v>
@@ -3679,7 +3679,7 @@
         <v>124</v>
       </c>
       <c r="W28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X28" t="s">
         <v>124</v>
@@ -3694,7 +3694,7 @@
         <v>124</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.001969919</v>
+        <v>0.053937877</v>
       </c>
       <c r="AC28" t="s">
         <v>217</v>
@@ -3741,7 +3741,7 @@
         <v>134</v>
       </c>
       <c r="L29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M29" t="s">
         <v>124</v>
@@ -3774,7 +3774,7 @@
         <v>124</v>
       </c>
       <c r="W29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X29" t="s">
         <v>124</v>
@@ -3789,7 +3789,7 @@
         <v>124</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.002498876</v>
+        <v>0.045285979</v>
       </c>
       <c r="AC29" t="s">
         <v>217</v>
@@ -3836,7 +3836,7 @@
         <v>134</v>
       </c>
       <c r="L30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M30" t="s">
         <v>124</v>
@@ -3869,7 +3869,7 @@
         <v>124</v>
       </c>
       <c r="W30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X30" t="s">
         <v>124</v>
@@ -3884,7 +3884,7 @@
         <v>124</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.002380284</v>
+        <v>0.009470893</v>
       </c>
       <c r="AC30" t="s">
         <v>217</v>
@@ -3931,7 +3931,7 @@
         <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s">
         <v>124</v>
@@ -3964,7 +3964,7 @@
         <v>124</v>
       </c>
       <c r="W31" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="X31" t="s">
         <v>124</v>
@@ -3979,7 +3979,7 @@
         <v>124</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.002438007</v>
+        <v>0.010118339</v>
       </c>
       <c r="AC31" t="s">
         <v>217</v>
@@ -4026,7 +4026,7 @@
         <v>134</v>
       </c>
       <c r="L32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M32" t="s">
         <v>124</v>
@@ -4059,7 +4059,7 @@
         <v>124</v>
       </c>
       <c r="W32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="X32" t="s">
         <v>124</v>
@@ -4074,7 +4074,7 @@
         <v>124</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.002537856</v>
+        <v>0.009772012</v>
       </c>
       <c r="AC32" t="s">
         <v>217</v>
@@ -4121,7 +4121,7 @@
         <v>134</v>
       </c>
       <c r="L33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M33" t="s">
         <v>124</v>
@@ -4154,7 +4154,7 @@
         <v>124</v>
       </c>
       <c r="W33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="X33" t="s">
         <v>124</v>
@@ -4169,7 +4169,7 @@
         <v>124</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002326722</v>
+        <v>0.0110654</v>
       </c>
       <c r="AC33" t="s">
         <v>217</v>
@@ -4216,7 +4216,7 @@
         <v>134</v>
       </c>
       <c r="L34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s">
         <v>124</v>
@@ -4249,7 +4249,7 @@
         <v>124</v>
       </c>
       <c r="W34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X34" t="s">
         <v>124</v>
@@ -4264,7 +4264,7 @@
         <v>124</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.002350475</v>
+        <v>0.009810562</v>
       </c>
       <c r="AC34" t="s">
         <v>217</v>
@@ -4311,7 +4311,7 @@
         <v>134</v>
       </c>
       <c r="L35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M35" t="s">
         <v>124</v>
@@ -4344,7 +4344,7 @@
         <v>124</v>
       </c>
       <c r="W35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="X35" t="s">
         <v>124</v>
@@ -4359,7 +4359,7 @@
         <v>124</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.008188906</v>
+        <v>0.011313336</v>
       </c>
       <c r="AC35" t="s">
         <v>217</v>
@@ -4406,7 +4406,7 @@
         <v>134</v>
       </c>
       <c r="L36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M36" t="s">
         <v>124</v>
@@ -4439,7 +4439,7 @@
         <v>124</v>
       </c>
       <c r="W36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X36" t="s">
         <v>124</v>
@@ -4454,7 +4454,7 @@
         <v>124</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.007518359</v>
+        <v>0.068002978</v>
       </c>
       <c r="AC36" t="s">
         <v>217</v>
@@ -4501,7 +4501,7 @@
         <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M37" t="s">
         <v>124</v>
@@ -4534,7 +4534,7 @@
         <v>124</v>
       </c>
       <c r="W37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="X37" t="s">
         <v>124</v>
@@ -4549,7 +4549,7 @@
         <v>124</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.032248067</v>
+        <v>0.0786813</v>
       </c>
       <c r="AC37" t="s">
         <v>217</v>
@@ -4596,7 +4596,7 @@
         <v>134</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s">
         <v>124</v>
@@ -4629,7 +4629,7 @@
         <v>124</v>
       </c>
       <c r="W38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X38" t="s">
         <v>124</v>
@@ -4644,7 +4644,7 @@
         <v>124</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.025999723</v>
+        <v>0.009485241</v>
       </c>
       <c r="AC38" t="s">
         <v>217</v>
@@ -4691,7 +4691,7 @@
         <v>134</v>
       </c>
       <c r="L39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M39" t="s">
         <v>124</v>
@@ -4724,7 +4724,7 @@
         <v>124</v>
       </c>
       <c r="W39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X39" t="s">
         <v>124</v>
@@ -4739,7 +4739,7 @@
         <v>124</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.00559294</v>
+        <v>0.01111347</v>
       </c>
       <c r="AC39" t="s">
         <v>217</v>
@@ -4786,7 +4786,7 @@
         <v>134</v>
       </c>
       <c r="L40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s">
         <v>124</v>
@@ -4819,7 +4819,7 @@
         <v>124</v>
       </c>
       <c r="W40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X40" t="s">
         <v>124</v>
@@ -4834,7 +4834,7 @@
         <v>124</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.005558036</v>
+        <v>0.009401165</v>
       </c>
       <c r="AC40" t="s">
         <v>217</v>
@@ -4914,7 +4914,7 @@
         <v>124</v>
       </c>
       <c r="W41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="X41" t="s">
         <v>124</v>
@@ -4929,7 +4929,7 @@
         <v>124</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.006213158</v>
+        <v>0.011288919</v>
       </c>
       <c r="AC41" t="s">
         <v>217</v>
@@ -5009,7 +5009,7 @@
         <v>124</v>
       </c>
       <c r="W42" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="X42" t="s">
         <v>124</v>
@@ -5024,7 +5024,7 @@
         <v>124</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.043013646</v>
+        <v>0.009361505</v>
       </c>
       <c r="AC42" t="s">
         <v>217</v>
@@ -5104,7 +5104,7 @@
         <v>124</v>
       </c>
       <c r="W43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="X43" t="s">
         <v>124</v>
@@ -5119,7 +5119,7 @@
         <v>124</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.049322095</v>
+        <v>0.011095322</v>
       </c>
       <c r="AC43" t="s">
         <v>217</v>
@@ -5199,7 +5199,7 @@
         <v>124</v>
       </c>
       <c r="W44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="X44" t="s">
         <v>124</v>
@@ -5214,7 +5214,7 @@
         <v>124</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.006954877</v>
+        <v>0.009416124</v>
       </c>
       <c r="AC44" t="s">
         <v>217</v>
@@ -5261,7 +5261,7 @@
         <v>134</v>
       </c>
       <c r="L45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s">
         <v>124</v>
@@ -5294,7 +5294,7 @@
         <v>124</v>
       </c>
       <c r="W45" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="X45" t="s">
         <v>124</v>
@@ -5309,7 +5309,7 @@
         <v>124</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.007374454</v>
+        <v>0.004239412</v>
       </c>
       <c r="AC45" t="s">
         <v>217</v>
@@ -5389,7 +5389,7 @@
         <v>124</v>
       </c>
       <c r="W46" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X46" t="s">
         <v>124</v>
@@ -5404,7 +5404,7 @@
         <v>124</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.007274797</v>
+        <v>0.014288217</v>
       </c>
       <c r="AC46" t="s">
         <v>217</v>
@@ -5484,7 +5484,7 @@
         <v>124</v>
       </c>
       <c r="W47" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X47" t="s">
         <v>124</v>
@@ -5499,7 +5499,7 @@
         <v>124</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.007935862</v>
+        <v>0.015222432</v>
       </c>
       <c r="AC47" t="s">
         <v>217</v>
@@ -5579,7 +5579,7 @@
         <v>124</v>
       </c>
       <c r="W48" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="X48" t="s">
         <v>124</v>
@@ -5594,7 +5594,7 @@
         <v>124</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.007080464</v>
+        <v>0.014039795</v>
       </c>
       <c r="AC48" t="s">
         <v>217</v>
@@ -5641,7 +5641,7 @@
         <v>134</v>
       </c>
       <c r="L49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s">
         <v>124</v>
@@ -5674,7 +5674,7 @@
         <v>124</v>
       </c>
       <c r="W49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X49" t="s">
         <v>124</v>
@@ -5689,7 +5689,7 @@
         <v>124</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.007857064</v>
+        <v>0.031932413</v>
       </c>
       <c r="AC49" t="s">
         <v>217</v>
@@ -5736,7 +5736,7 @@
         <v>134</v>
       </c>
       <c r="L50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M50" t="s">
         <v>124</v>
@@ -5769,7 +5769,7 @@
         <v>124</v>
       </c>
       <c r="W50" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="X50" t="s">
         <v>124</v>
@@ -5784,7 +5784,7 @@
         <v>124</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.006690431</v>
+        <v>0.024544266</v>
       </c>
       <c r="AC50" t="s">
         <v>217</v>
@@ -5831,7 +5831,7 @@
         <v>134</v>
       </c>
       <c r="L51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M51" t="s">
         <v>124</v>
@@ -5864,7 +5864,7 @@
         <v>124</v>
       </c>
       <c r="W51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="X51" t="s">
         <v>124</v>
@@ -5879,7 +5879,7 @@
         <v>124</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.007498418</v>
+        <v>0.005459863</v>
       </c>
       <c r="AC51" t="s">
         <v>217</v>
@@ -5926,7 +5926,7 @@
         <v>134</v>
       </c>
       <c r="L52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M52" t="s">
         <v>124</v>
@@ -5959,7 +5959,7 @@
         <v>124</v>
       </c>
       <c r="W52" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="X52" t="s">
         <v>124</v>
@@ -5974,7 +5974,7 @@
         <v>124</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.023058507</v>
+        <v>0.004400825</v>
       </c>
       <c r="AC52" t="s">
         <v>217</v>
@@ -6021,7 +6021,7 @@
         <v>134</v>
       </c>
       <c r="L53" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M53" t="s">
         <v>124</v>
@@ -6054,7 +6054,7 @@
         <v>124</v>
       </c>
       <c r="W53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X53" t="s">
         <v>124</v>
@@ -6069,7 +6069,7 @@
         <v>124</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.024250153</v>
+        <v>0.005624833</v>
       </c>
       <c r="AC53" t="s">
         <v>217</v>
@@ -6149,7 +6149,7 @@
         <v>124</v>
       </c>
       <c r="W54" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="X54" t="s">
         <v>124</v>
@@ -6164,7 +6164,7 @@
         <v>124</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.006514123</v>
+        <v>0.004944183</v>
       </c>
       <c r="AC54" t="s">
         <v>217</v>
@@ -6244,7 +6244,7 @@
         <v>124</v>
       </c>
       <c r="W55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X55" t="s">
         <v>124</v>
@@ -6259,7 +6259,7 @@
         <v>124</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.022727369</v>
+        <v>0.005789925</v>
       </c>
       <c r="AC55" t="s">
         <v>217</v>
@@ -6339,7 +6339,7 @@
         <v>124</v>
       </c>
       <c r="W56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X56" t="s">
         <v>124</v>
@@ -6354,7 +6354,7 @@
         <v>124</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.021674355</v>
+        <v>0.005426907</v>
       </c>
       <c r="AC56" t="s">
         <v>217</v>
@@ -6434,7 +6434,7 @@
         <v>124</v>
       </c>
       <c r="W57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="X57" t="s">
         <v>124</v>
@@ -6449,7 +6449,7 @@
         <v>124</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.009812113</v>
+        <v>0.045655947</v>
       </c>
       <c r="AC57" t="s">
         <v>217</v>
@@ -6529,7 +6529,7 @@
         <v>124</v>
       </c>
       <c r="W58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="X58" t="s">
         <v>124</v>
@@ -6544,7 +6544,7 @@
         <v>124</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.005686357</v>
+        <v>0.042025038</v>
       </c>
       <c r="AC58" t="s">
         <v>217</v>
@@ -6624,7 +6624,7 @@
         <v>124</v>
       </c>
       <c r="W59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X59" t="s">
         <v>124</v>
@@ -6639,7 +6639,7 @@
         <v>124</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.001480606</v>
+        <v>0.006878595</v>
       </c>
       <c r="AC59" t="s">
         <v>217</v>
@@ -6719,7 +6719,7 @@
         <v>124</v>
       </c>
       <c r="W60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X60" t="s">
         <v>124</v>
@@ -6734,7 +6734,7 @@
         <v>124</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.000781829</v>
+        <v>0.006495451</v>
       </c>
       <c r="AC60" t="s">
         <v>217</v>
@@ -6814,7 +6814,7 @@
         <v>124</v>
       </c>
       <c r="W61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X61" t="s">
         <v>124</v>
@@ -6829,7 +6829,7 @@
         <v>124</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.001467165</v>
+        <v>0.006971473</v>
       </c>
       <c r="AC61" t="s">
         <v>217</v>
@@ -6909,7 +6909,7 @@
         <v>124</v>
       </c>
       <c r="W62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X62" t="s">
         <v>124</v>
@@ -6924,7 +6924,7 @@
         <v>124</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.000989828</v>
+        <v>0.006923147</v>
       </c>
       <c r="AC62" t="s">
         <v>217</v>
@@ -7004,7 +7004,7 @@
         <v>124</v>
       </c>
       <c r="W63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="X63" t="s">
         <v>124</v>
@@ -7019,7 +7019,7 @@
         <v>124</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.001588894</v>
+        <v>0.032248067</v>
       </c>
       <c r="AC63" t="s">
         <v>217</v>
@@ -7099,7 +7099,7 @@
         <v>124</v>
       </c>
       <c r="W64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="X64" t="s">
         <v>124</v>
@@ -7114,7 +7114,7 @@
         <v>124</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.00117488</v>
+        <v>0.025999723</v>
       </c>
       <c r="AC64" t="s">
         <v>217</v>
@@ -7194,7 +7194,7 @@
         <v>124</v>
       </c>
       <c r="W65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X65" t="s">
         <v>124</v>
@@ -7209,7 +7209,7 @@
         <v>124</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.01462736</v>
+        <v>0.00559294</v>
       </c>
       <c r="AC65" t="s">
         <v>217</v>
@@ -7289,7 +7289,7 @@
         <v>124</v>
       </c>
       <c r="W66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X66" t="s">
         <v>124</v>
@@ -7304,7 +7304,7 @@
         <v>124</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.012185883</v>
+        <v>0.005558036</v>
       </c>
       <c r="AC66" t="s">
         <v>217</v>
@@ -7351,7 +7351,7 @@
         <v>134</v>
       </c>
       <c r="L67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s">
         <v>124</v>
@@ -7384,7 +7384,7 @@
         <v>124</v>
       </c>
       <c r="W67" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="X67" t="s">
         <v>124</v>
@@ -7399,7 +7399,7 @@
         <v>124</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.015472817</v>
+        <v>0.005548685</v>
       </c>
       <c r="AC67" t="s">
         <v>217</v>
@@ -7446,7 +7446,7 @@
         <v>134</v>
       </c>
       <c r="L68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M68" t="s">
         <v>124</v>
@@ -7479,7 +7479,7 @@
         <v>124</v>
       </c>
       <c r="W68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X68" t="s">
         <v>124</v>
@@ -7494,7 +7494,7 @@
         <v>124</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.100334681</v>
+        <v>0.005703369</v>
       </c>
       <c r="AC68" t="s">
         <v>217</v>
@@ -7541,7 +7541,7 @@
         <v>134</v>
       </c>
       <c r="L69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M69" t="s">
         <v>124</v>
@@ -7589,7 +7589,7 @@
         <v>124</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.114579297</v>
+        <v>0.005512073</v>
       </c>
       <c r="AC69" t="s">
         <v>217</v>
@@ -7636,7 +7636,7 @@
         <v>134</v>
       </c>
       <c r="L70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M70" t="s">
         <v>124</v>
@@ -7669,7 +7669,7 @@
         <v>124</v>
       </c>
       <c r="W70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X70" t="s">
         <v>124</v>
@@ -7684,7 +7684,7 @@
         <v>124</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.015273349</v>
+        <v>0.006213158</v>
       </c>
       <c r="AC70" t="s">
         <v>217</v>
@@ -7731,7 +7731,7 @@
         <v>134</v>
       </c>
       <c r="L71" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M71" t="s">
         <v>124</v>
@@ -7779,7 +7779,7 @@
         <v>124</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.017715821</v>
+        <v>0.043013646</v>
       </c>
       <c r="AC71" t="s">
         <v>217</v>
@@ -7826,7 +7826,7 @@
         <v>134</v>
       </c>
       <c r="L72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M72" t="s">
         <v>124</v>
@@ -7859,7 +7859,7 @@
         <v>124</v>
       </c>
       <c r="W72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X72" t="s">
         <v>124</v>
@@ -7874,7 +7874,7 @@
         <v>124</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.015385153</v>
+        <v>0.049322095</v>
       </c>
       <c r="AC72" t="s">
         <v>217</v>
@@ -7921,7 +7921,7 @@
         <v>134</v>
       </c>
       <c r="L73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M73" t="s">
         <v>124</v>
@@ -7969,7 +7969,7 @@
         <v>124</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.018102119</v>
+        <v>0.006954877</v>
       </c>
       <c r="AC73" t="s">
         <v>217</v>
@@ -8016,7 +8016,7 @@
         <v>134</v>
       </c>
       <c r="L74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M74" t="s">
         <v>124</v>
@@ -8049,7 +8049,7 @@
         <v>124</v>
       </c>
       <c r="W74" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X74" t="s">
         <v>124</v>
@@ -8064,7 +8064,7 @@
         <v>124</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.015358091</v>
+        <v>0.007374454</v>
       </c>
       <c r="AC74" t="s">
         <v>217</v>
@@ -8111,7 +8111,7 @@
         <v>134</v>
       </c>
       <c r="L75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M75" t="s">
         <v>124</v>
@@ -8159,7 +8159,7 @@
         <v>124</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.017745472</v>
+        <v>0.007274797</v>
       </c>
       <c r="AC75" t="s">
         <v>217</v>
@@ -8206,7 +8206,7 @@
         <v>134</v>
       </c>
       <c r="L76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M76" t="s">
         <v>124</v>
@@ -8239,7 +8239,7 @@
         <v>124</v>
       </c>
       <c r="W76" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X76" t="s">
         <v>124</v>
@@ -8254,7 +8254,7 @@
         <v>124</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.015234293</v>
+        <v>0.007935862</v>
       </c>
       <c r="AC76" t="s">
         <v>217</v>
@@ -8301,7 +8301,7 @@
         <v>134</v>
       </c>
       <c r="L77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M77" t="s">
         <v>124</v>
@@ -8349,7 +8349,7 @@
         <v>124</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.017650786</v>
+        <v>0.007080464</v>
       </c>
       <c r="AC77" t="s">
         <v>217</v>
@@ -8396,7 +8396,7 @@
         <v>134</v>
       </c>
       <c r="L78" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M78" t="s">
         <v>124</v>
@@ -8429,7 +8429,7 @@
         <v>124</v>
       </c>
       <c r="W78" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X78" t="s">
         <v>124</v>
@@ -8444,7 +8444,7 @@
         <v>124</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.060152037</v>
+        <v>0.007857064</v>
       </c>
       <c r="AC78" t="s">
         <v>217</v>
@@ -8491,7 +8491,7 @@
         <v>134</v>
       </c>
       <c r="L79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M79" t="s">
         <v>124</v>
@@ -8539,7 +8539,7 @@
         <v>124</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.062337475</v>
+        <v>0.006690431</v>
       </c>
       <c r="AC79" t="s">
         <v>217</v>
@@ -8619,7 +8619,7 @@
         <v>124</v>
       </c>
       <c r="W80" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X80" t="s">
         <v>124</v>
@@ -8634,7 +8634,7 @@
         <v>124</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.010758853</v>
+        <v>0.007498418</v>
       </c>
       <c r="AC80" t="s">
         <v>217</v>
@@ -8681,7 +8681,7 @@
         <v>134</v>
       </c>
       <c r="L81" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M81" t="s">
         <v>124</v>
@@ -8714,7 +8714,7 @@
         <v>124</v>
       </c>
       <c r="W81" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="X81" t="s">
         <v>124</v>
@@ -8729,7 +8729,7 @@
         <v>124</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.0110654</v>
+        <v>0.023058507</v>
       </c>
       <c r="AC81" t="s">
         <v>217</v>
@@ -8776,7 +8776,7 @@
         <v>134</v>
       </c>
       <c r="L82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M82" t="s">
         <v>124</v>
@@ -8809,7 +8809,7 @@
         <v>124</v>
       </c>
       <c r="W82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X82" t="s">
         <v>124</v>
@@ -8824,7 +8824,7 @@
         <v>124</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.009810562</v>
+        <v>0.024250153</v>
       </c>
       <c r="AC82" t="s">
         <v>217</v>
@@ -8904,7 +8904,7 @@
         <v>124</v>
       </c>
       <c r="W83" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="X83" t="s">
         <v>124</v>
@@ -8919,7 +8919,7 @@
         <v>124</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.011313336</v>
+        <v>0.006514123</v>
       </c>
       <c r="AC83" t="s">
         <v>217</v>
@@ -8999,7 +8999,7 @@
         <v>124</v>
       </c>
       <c r="W84" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X84" t="s">
         <v>124</v>
@@ -9014,7 +9014,7 @@
         <v>124</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.068002978</v>
+        <v>0.022727369</v>
       </c>
       <c r="AC84" t="s">
         <v>217</v>
@@ -9094,7 +9094,7 @@
         <v>124</v>
       </c>
       <c r="W85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X85" t="s">
         <v>124</v>
@@ -9109,7 +9109,7 @@
         <v>124</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.0786813</v>
+        <v>0.021674355</v>
       </c>
       <c r="AC85" t="s">
         <v>217</v>
@@ -9189,7 +9189,7 @@
         <v>124</v>
       </c>
       <c r="W86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X86" t="s">
         <v>124</v>
@@ -9204,7 +9204,7 @@
         <v>124</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.009485241</v>
+        <v>0.009812113</v>
       </c>
       <c r="AC86" t="s">
         <v>217</v>
@@ -9284,7 +9284,7 @@
         <v>124</v>
       </c>
       <c r="W87" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X87" t="s">
         <v>124</v>
@@ -9299,7 +9299,7 @@
         <v>124</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.01111347</v>
+        <v>0.005686357</v>
       </c>
       <c r="AC87" t="s">
         <v>217</v>
@@ -9379,7 +9379,7 @@
         <v>124</v>
       </c>
       <c r="W88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X88" t="s">
         <v>124</v>
@@ -9394,7 +9394,7 @@
         <v>124</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.009401165</v>
+        <v>0.001480606</v>
       </c>
       <c r="AC88" t="s">
         <v>217</v>
@@ -9474,7 +9474,7 @@
         <v>124</v>
       </c>
       <c r="W89" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X89" t="s">
         <v>124</v>
@@ -9489,7 +9489,7 @@
         <v>124</v>
       </c>
       <c r="AB89" t="n">
-        <v>0.011288919</v>
+        <v>0.000781829</v>
       </c>
       <c r="AC89" t="s">
         <v>217</v>
@@ -9569,7 +9569,7 @@
         <v>124</v>
       </c>
       <c r="W90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X90" t="s">
         <v>124</v>
@@ -9584,7 +9584,7 @@
         <v>124</v>
       </c>
       <c r="AB90" t="n">
-        <v>0.009361505</v>
+        <v>0.001467165</v>
       </c>
       <c r="AC90" t="s">
         <v>217</v>
@@ -9664,7 +9664,7 @@
         <v>124</v>
       </c>
       <c r="W91" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X91" t="s">
         <v>124</v>
@@ -9679,7 +9679,7 @@
         <v>124</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.011095322</v>
+        <v>0.000989828</v>
       </c>
       <c r="AC91" t="s">
         <v>217</v>
@@ -9759,7 +9759,7 @@
         <v>124</v>
       </c>
       <c r="W92" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="X92" t="s">
         <v>124</v>
@@ -9774,7 +9774,7 @@
         <v>124</v>
       </c>
       <c r="AB92" t="n">
-        <v>0.009416124</v>
+        <v>0.001588894</v>
       </c>
       <c r="AC92" t="s">
         <v>217</v>
@@ -9821,7 +9821,7 @@
         <v>134</v>
       </c>
       <c r="L93" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M93" t="s">
         <v>124</v>
@@ -9854,7 +9854,7 @@
         <v>124</v>
       </c>
       <c r="W93" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="X93" t="s">
         <v>124</v>
@@ -9869,7 +9869,7 @@
         <v>124</v>
       </c>
       <c r="AB93" t="n">
-        <v>0.004239412</v>
+        <v>0.00117488</v>
       </c>
       <c r="AC93" t="s">
         <v>217</v>
@@ -9964,7 +9964,7 @@
         <v>124</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.036646967</v>
+        <v>0.01462736</v>
       </c>
       <c r="AC94" t="s">
         <v>217</v>
@@ -10059,7 +10059,7 @@
         <v>124</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.037675262</v>
+        <v>0.012185883</v>
       </c>
       <c r="AC95" t="s">
         <v>217</v>
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="L96" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M96" t="s">
         <v>124</v>
@@ -10139,7 +10139,7 @@
         <v>124</v>
       </c>
       <c r="W96" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="X96" t="s">
         <v>124</v>
@@ -10154,7 +10154,7 @@
         <v>124</v>
       </c>
       <c r="AB96" t="n">
-        <v>0.02187069</v>
+        <v>0.015472817</v>
       </c>
       <c r="AC96" t="s">
         <v>217</v>
@@ -10201,7 +10201,7 @@
         <v>134</v>
       </c>
       <c r="L97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M97" t="s">
         <v>124</v>
@@ -10249,7 +10249,7 @@
         <v>124</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.015902671</v>
+        <v>0.100334681</v>
       </c>
       <c r="AC97" t="s">
         <v>217</v>
@@ -10296,7 +10296,7 @@
         <v>134</v>
       </c>
       <c r="L98" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M98" t="s">
         <v>124</v>
@@ -10329,7 +10329,7 @@
         <v>124</v>
       </c>
       <c r="W98" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X98" t="s">
         <v>124</v>
@@ -10344,7 +10344,7 @@
         <v>124</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.003792878</v>
+        <v>0.114579297</v>
       </c>
       <c r="AC98" t="s">
         <v>217</v>
@@ -10391,7 +10391,7 @@
         <v>134</v>
       </c>
       <c r="L99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M99" t="s">
         <v>124</v>
@@ -10439,7 +10439,7 @@
         <v>124</v>
       </c>
       <c r="AB99" t="n">
-        <v>0.002924553</v>
+        <v>0.015273349</v>
       </c>
       <c r="AC99" t="s">
         <v>217</v>
@@ -10486,7 +10486,7 @@
         <v>134</v>
       </c>
       <c r="L100" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M100" t="s">
         <v>124</v>
@@ -10519,7 +10519,7 @@
         <v>124</v>
       </c>
       <c r="W100" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X100" t="s">
         <v>124</v>
@@ -10534,7 +10534,7 @@
         <v>124</v>
       </c>
       <c r="AB100" t="n">
-        <v>0.003855268</v>
+        <v>0.017715821</v>
       </c>
       <c r="AC100" t="s">
         <v>217</v>
@@ -10581,7 +10581,7 @@
         <v>134</v>
       </c>
       <c r="L101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M101" t="s">
         <v>124</v>
@@ -10629,7 +10629,7 @@
         <v>124</v>
       </c>
       <c r="AB101" t="n">
-        <v>0.003281807</v>
+        <v>0.015385153</v>
       </c>
       <c r="AC101" t="s">
         <v>217</v>
@@ -10676,7 +10676,7 @@
         <v>134</v>
       </c>
       <c r="L102" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M102" t="s">
         <v>124</v>
@@ -10709,7 +10709,7 @@
         <v>124</v>
       </c>
       <c r="W102" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X102" t="s">
         <v>124</v>
@@ -10724,7 +10724,7 @@
         <v>124</v>
       </c>
       <c r="AB102" t="n">
-        <v>0.00392837</v>
+        <v>0.018102119</v>
       </c>
       <c r="AC102" t="s">
         <v>217</v>
@@ -10771,7 +10771,7 @@
         <v>134</v>
       </c>
       <c r="L103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M103" t="s">
         <v>124</v>
@@ -10819,7 +10819,7 @@
         <v>124</v>
       </c>
       <c r="AB103" t="n">
-        <v>0.003610349</v>
+        <v>0.015358091</v>
       </c>
       <c r="AC103" t="s">
         <v>217</v>
@@ -10866,7 +10866,7 @@
         <v>134</v>
       </c>
       <c r="L104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M104" t="s">
         <v>124</v>
@@ -10899,7 +10899,7 @@
         <v>124</v>
       </c>
       <c r="W104" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X104" t="s">
         <v>124</v>
@@ -10914,7 +10914,7 @@
         <v>124</v>
       </c>
       <c r="AB104" t="n">
-        <v>0.029224619</v>
+        <v>0.017745472</v>
       </c>
       <c r="AC104" t="s">
         <v>217</v>
@@ -10961,7 +10961,7 @@
         <v>134</v>
       </c>
       <c r="L105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M105" t="s">
         <v>124</v>
@@ -11009,7 +11009,7 @@
         <v>124</v>
       </c>
       <c r="AB105" t="n">
-        <v>0.030742214</v>
+        <v>0.015234293</v>
       </c>
       <c r="AC105" t="s">
         <v>217</v>
@@ -11089,7 +11089,7 @@
         <v>124</v>
       </c>
       <c r="W106" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="X106" t="s">
         <v>124</v>
@@ -11104,7 +11104,7 @@
         <v>124</v>
       </c>
       <c r="AB106" t="n">
-        <v>0.024544266</v>
+        <v>0.017650786</v>
       </c>
       <c r="AC106" t="s">
         <v>217</v>
@@ -11199,7 +11199,7 @@
         <v>124</v>
       </c>
       <c r="AB107" t="n">
-        <v>0.005459863</v>
+        <v>0.060152037</v>
       </c>
       <c r="AC107" t="s">
         <v>217</v>
@@ -11294,7 +11294,7 @@
         <v>124</v>
       </c>
       <c r="AB108" t="n">
-        <v>0.004400825</v>
+        <v>0.062337475</v>
       </c>
       <c r="AC108" t="s">
         <v>217</v>
@@ -11341,7 +11341,7 @@
         <v>134</v>
       </c>
       <c r="L109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M109" t="s">
         <v>124</v>
@@ -11374,7 +11374,7 @@
         <v>124</v>
       </c>
       <c r="W109" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="X109" t="s">
         <v>124</v>
@@ -11389,7 +11389,7 @@
         <v>124</v>
       </c>
       <c r="AB109" t="n">
-        <v>0.005624833</v>
+        <v>0.010758853</v>
       </c>
       <c r="AC109" t="s">
         <v>217</v>
@@ -11436,7 +11436,7 @@
         <v>134</v>
       </c>
       <c r="L110" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M110" t="s">
         <v>124</v>
@@ -11484,7 +11484,7 @@
         <v>124</v>
       </c>
       <c r="AB110" t="n">
-        <v>0.004944183</v>
+        <v>0.036646967</v>
       </c>
       <c r="AC110" t="s">
         <v>217</v>
@@ -11531,7 +11531,7 @@
         <v>134</v>
       </c>
       <c r="L111" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M111" t="s">
         <v>124</v>
@@ -11564,7 +11564,7 @@
         <v>124</v>
       </c>
       <c r="W111" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X111" t="s">
         <v>124</v>
@@ -11579,7 +11579,7 @@
         <v>124</v>
       </c>
       <c r="AB111" t="n">
-        <v>0.005789925</v>
+        <v>0.037675262</v>
       </c>
       <c r="AC111" t="s">
         <v>217</v>
@@ -11626,7 +11626,7 @@
         <v>134</v>
       </c>
       <c r="L112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M112" t="s">
         <v>124</v>
@@ -11674,7 +11674,7 @@
         <v>124</v>
       </c>
       <c r="AB112" t="n">
-        <v>0.005426907</v>
+        <v>0.02187069</v>
       </c>
       <c r="AC112" t="s">
         <v>217</v>
@@ -11721,7 +11721,7 @@
         <v>134</v>
       </c>
       <c r="L113" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M113" t="s">
         <v>124</v>
@@ -11754,7 +11754,7 @@
         <v>124</v>
       </c>
       <c r="W113" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X113" t="s">
         <v>124</v>
@@ -11769,7 +11769,7 @@
         <v>124</v>
       </c>
       <c r="AB113" t="n">
-        <v>0.045655947</v>
+        <v>0.015902671</v>
       </c>
       <c r="AC113" t="s">
         <v>217</v>
@@ -11816,7 +11816,7 @@
         <v>134</v>
       </c>
       <c r="L114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M114" t="s">
         <v>124</v>
@@ -11864,7 +11864,7 @@
         <v>124</v>
       </c>
       <c r="AB114" t="n">
-        <v>0.042025038</v>
+        <v>0.003792878</v>
       </c>
       <c r="AC114" t="s">
         <v>217</v>
@@ -11911,7 +11911,7 @@
         <v>134</v>
       </c>
       <c r="L115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M115" t="s">
         <v>124</v>
@@ -11944,7 +11944,7 @@
         <v>124</v>
       </c>
       <c r="W115" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X115" t="s">
         <v>124</v>
@@ -11959,7 +11959,7 @@
         <v>124</v>
       </c>
       <c r="AB115" t="n">
-        <v>0.006878595</v>
+        <v>0.002924553</v>
       </c>
       <c r="AC115" t="s">
         <v>217</v>
@@ -12006,7 +12006,7 @@
         <v>134</v>
       </c>
       <c r="L116" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M116" t="s">
         <v>124</v>
@@ -12054,7 +12054,7 @@
         <v>124</v>
       </c>
       <c r="AB116" t="n">
-        <v>0.006495451</v>
+        <v>0.003855268</v>
       </c>
       <c r="AC116" t="s">
         <v>217</v>
@@ -12101,7 +12101,7 @@
         <v>134</v>
       </c>
       <c r="L117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M117" t="s">
         <v>124</v>
@@ -12134,7 +12134,7 @@
         <v>124</v>
       </c>
       <c r="W117" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X117" t="s">
         <v>124</v>
@@ -12149,7 +12149,7 @@
         <v>124</v>
       </c>
       <c r="AB117" t="n">
-        <v>0.006971473</v>
+        <v>0.003281807</v>
       </c>
       <c r="AC117" t="s">
         <v>217</v>
@@ -12196,7 +12196,7 @@
         <v>134</v>
       </c>
       <c r="L118" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M118" t="s">
         <v>124</v>
@@ -12244,7 +12244,7 @@
         <v>124</v>
       </c>
       <c r="AB118" t="n">
-        <v>0.006923147</v>
+        <v>0.00392837</v>
       </c>
       <c r="AC118" t="s">
         <v>217</v>
@@ -12291,7 +12291,7 @@
         <v>134</v>
       </c>
       <c r="L119" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M119" t="s">
         <v>124</v>
@@ -12324,7 +12324,7 @@
         <v>124</v>
       </c>
       <c r="W119" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X119" t="s">
         <v>124</v>
@@ -12339,7 +12339,7 @@
         <v>124</v>
       </c>
       <c r="AB119" t="n">
-        <v>0.005548685</v>
+        <v>0.003610349</v>
       </c>
       <c r="AC119" t="s">
         <v>217</v>
@@ -12386,7 +12386,7 @@
         <v>134</v>
       </c>
       <c r="L120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M120" t="s">
         <v>124</v>
@@ -12434,7 +12434,7 @@
         <v>124</v>
       </c>
       <c r="AB120" t="n">
-        <v>0.005703369</v>
+        <v>0.029224619</v>
       </c>
       <c r="AC120" t="s">
         <v>217</v>
@@ -12481,7 +12481,7 @@
         <v>134</v>
       </c>
       <c r="L121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M121" t="s">
         <v>124</v>
@@ -12514,7 +12514,7 @@
         <v>124</v>
       </c>
       <c r="W121" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="X121" t="s">
         <v>124</v>
@@ -12529,7 +12529,7 @@
         <v>124</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.005512073</v>
+        <v>0.030742214</v>
       </c>
       <c r="AC121" t="s">
         <v>217</v>
@@ -12635,7 +12635,7 @@
         <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F3" t="s">
         <v>239</v>
@@ -12705,7 +12705,7 @@
         <v>232</v>
       </c>
       <c r="E5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F5" t="s">
         <v>239</v>
@@ -12740,7 +12740,7 @@
         <v>232</v>
       </c>
       <c r="E6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F6" t="s">
         <v>239</v>
@@ -12775,7 +12775,7 @@
         <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F7" t="s">
         <v>239</v>
@@ -12790,7 +12790,7 @@
         <v>280</v>
       </c>
       <c r="J7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K7" t="s">
         <v>124</v>
@@ -12810,7 +12810,7 @@
         <v>232</v>
       </c>
       <c r="E8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F8" t="s">
         <v>239</v>
@@ -12825,7 +12825,7 @@
         <v>280</v>
       </c>
       <c r="J8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K8" t="s">
         <v>124</v>
@@ -12845,7 +12845,7 @@
         <v>232</v>
       </c>
       <c r="E9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F9" t="s">
         <v>239</v>
@@ -12860,7 +12860,7 @@
         <v>280</v>
       </c>
       <c r="J9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K9" t="s">
         <v>124</v>
@@ -12895,7 +12895,7 @@
         <v>280</v>
       </c>
       <c r="J10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K10" t="s">
         <v>124</v>
@@ -12915,7 +12915,7 @@
         <v>232</v>
       </c>
       <c r="E11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F11" t="s">
         <v>239</v>
@@ -12930,7 +12930,7 @@
         <v>280</v>
       </c>
       <c r="J11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K11" t="s">
         <v>124</v>
@@ -12950,7 +12950,7 @@
         <v>232</v>
       </c>
       <c r="E12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F12" t="s">
         <v>239</v>
@@ -12965,7 +12965,7 @@
         <v>280</v>
       </c>
       <c r="J12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K12" t="s">
         <v>124</v>
@@ -13000,7 +13000,7 @@
         <v>280</v>
       </c>
       <c r="J13" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K13" t="s">
         <v>124</v>
@@ -13008,34 +13008,34 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>234</v>
       </c>
       <c r="F14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H14" t="s">
         <v>257</v>
       </c>
       <c r="I14" t="s">
-        <v>124</v>
+        <v>280</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>283</v>
       </c>
       <c r="K14" t="s">
         <v>124</v>
@@ -13055,7 +13055,7 @@
         <v>232</v>
       </c>
       <c r="E15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F15" t="s">
         <v>239</v>
@@ -13070,7 +13070,7 @@
         <v>280</v>
       </c>
       <c r="J15" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K15" t="s">
         <v>124</v>
@@ -13090,7 +13090,7 @@
         <v>232</v>
       </c>
       <c r="E16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F16" t="s">
         <v>239</v>
@@ -13105,7 +13105,7 @@
         <v>280</v>
       </c>
       <c r="J16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K16" t="s">
         <v>124</v>
@@ -13125,7 +13125,7 @@
         <v>232</v>
       </c>
       <c r="E17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F17" t="s">
         <v>239</v>
@@ -13140,7 +13140,7 @@
         <v>280</v>
       </c>
       <c r="J17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K17" t="s">
         <v>124</v>
@@ -13160,7 +13160,7 @@
         <v>232</v>
       </c>
       <c r="E18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F18" t="s">
         <v>239</v>
@@ -13175,7 +13175,7 @@
         <v>280</v>
       </c>
       <c r="J18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K18" t="s">
         <v>124</v>
@@ -13195,7 +13195,7 @@
         <v>232</v>
       </c>
       <c r="E19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F19" t="s">
         <v>239</v>
@@ -13210,7 +13210,7 @@
         <v>280</v>
       </c>
       <c r="J19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K19" t="s">
         <v>124</v>
@@ -13245,7 +13245,7 @@
         <v>280</v>
       </c>
       <c r="J20" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K20" t="s">
         <v>124</v>
@@ -13256,7 +13256,7 @@
         <v>222</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
         <v>229</v>
@@ -13265,7 +13265,7 @@
         <v>232</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F21" t="s">
         <v>239</v>
@@ -13280,7 +13280,7 @@
         <v>280</v>
       </c>
       <c r="J21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K21" t="s">
         <v>124</v>
@@ -13300,7 +13300,7 @@
         <v>232</v>
       </c>
       <c r="E22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F22" t="s">
         <v>239</v>
@@ -13315,7 +13315,7 @@
         <v>280</v>
       </c>
       <c r="J22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K22" t="s">
         <v>124</v>
@@ -13335,7 +13335,7 @@
         <v>232</v>
       </c>
       <c r="E23" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F23" t="s">
         <v>239</v>
@@ -13350,7 +13350,7 @@
         <v>280</v>
       </c>
       <c r="J23" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K23" t="s">
         <v>124</v>
@@ -13370,7 +13370,7 @@
         <v>232</v>
       </c>
       <c r="E24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F24" t="s">
         <v>239</v>
@@ -13385,7 +13385,7 @@
         <v>280</v>
       </c>
       <c r="J24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K24" t="s">
         <v>124</v>
@@ -13396,7 +13396,7 @@
         <v>222</v>
       </c>
       <c r="B25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" t="s">
         <v>229</v>
@@ -13405,7 +13405,7 @@
         <v>232</v>
       </c>
       <c r="E25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F25" t="s">
         <v>239</v>
@@ -13420,7 +13420,7 @@
         <v>280</v>
       </c>
       <c r="J25" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K25" t="s">
         <v>124</v>
@@ -13428,34 +13428,34 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E26" t="s">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="F26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H26" t="s">
         <v>269</v>
       </c>
       <c r="I26" t="s">
-        <v>280</v>
+        <v>124</v>
       </c>
       <c r="J26" t="s">
-        <v>286</v>
+        <v>124</v>
       </c>
       <c r="K26" t="s">
         <v>124</v>
@@ -13475,7 +13475,7 @@
         <v>232</v>
       </c>
       <c r="E27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F27" t="s">
         <v>239</v>
@@ -13490,7 +13490,7 @@
         <v>280</v>
       </c>
       <c r="J27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K27" t="s">
         <v>124</v>
@@ -13510,7 +13510,7 @@
         <v>232</v>
       </c>
       <c r="E28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F28" t="s">
         <v>239</v>
@@ -13536,7 +13536,7 @@
         <v>222</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29" t="s">
         <v>229</v>
@@ -13560,7 +13560,7 @@
         <v>280</v>
       </c>
       <c r="J29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K29" t="s">
         <v>124</v>
@@ -13595,7 +13595,7 @@
         <v>280</v>
       </c>
       <c r="J30" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K30" t="s">
         <v>124</v>
@@ -13606,7 +13606,7 @@
         <v>222</v>
       </c>
       <c r="B31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C31" t="s">
         <v>229</v>
@@ -13615,7 +13615,7 @@
         <v>232</v>
       </c>
       <c r="E31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F31" t="s">
         <v>239</v>
@@ -13630,7 +13630,7 @@
         <v>280</v>
       </c>
       <c r="J31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K31" t="s">
         <v>124</v>
@@ -13650,7 +13650,7 @@
         <v>232</v>
       </c>
       <c r="E32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F32" t="s">
         <v>239</v>
@@ -13665,7 +13665,7 @@
         <v>280</v>
       </c>
       <c r="J32" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K32" t="s">
         <v>124</v>
@@ -13700,7 +13700,7 @@
         <v>280</v>
       </c>
       <c r="J33" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K33" t="s">
         <v>124</v>
@@ -13720,7 +13720,7 @@
         <v>232</v>
       </c>
       <c r="E34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F34" t="s">
         <v>239</v>
@@ -13755,7 +13755,7 @@
         <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F35" t="s">
         <v>239</v>
@@ -13770,7 +13770,7 @@
         <v>280</v>
       </c>
       <c r="J35" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K35" t="s">
         <v>124</v>
